--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140;VGASN0724QA9131</t>
+          <t>VGASN0725QA7080;VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830;00V07242025QA9201;00V07242025QA7252;00V07242025QA5793</t>
+          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140;VGASN0724QA9131</t>
+          <t>VGASN0725QA7080;VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830;00V07242025QA9201;00V07242025QA7252;00V07242025QA5793</t>
+          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140;VGASN0724QA9131</t>
+          <t>VGASN0725QA7080;VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830;00V07242025QA9201;00V07242025QA7252;00V07242025QA5793</t>
+          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140;VGASN0724QA9131</t>
+          <t>VGASN0725QA7080;VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830;00V07242025QA9201;00V07242025QA7252;00V07242025QA5793</t>
+          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140;VGASN0724QA9131</t>
+          <t>VGASN0725QA7080;VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830;00V07242025QA9201;00V07242025QA7252;00V07242025QA5793</t>
+          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0724QA7140;VGASN0724QA9131</t>
+          <t>VGASN0725QA7080;VGASN0725QA9771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07242025QA2830;00V07242025QA9201;00V07242025QA7252;00V07242025QA5793</t>
+          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080;VGASN0725QA9771</t>
+          <t>VGASN0725QA7840;VGASN0725QA9531</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
+          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080;VGASN0725QA9771</t>
+          <t>VGASN0725QA7840;VGASN0725QA9531</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
+          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080;VGASN0725QA9771</t>
+          <t>VGASN0725QA7840;VGASN0725QA9531</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
+          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080;VGASN0725QA9771</t>
+          <t>VGASN0725QA7840;VGASN0725QA9531</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
+          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080;VGASN0725QA9771</t>
+          <t>VGASN0725QA7840;VGASN0725QA9531</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
+          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7080;VGASN0725QA9771</t>
+          <t>VGASN0725QA7840;VGASN0725QA9531</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA5420;00V07252025QA5681;00V07252025QA8922;00V07252025QA2143</t>
+          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840;VGASN0725QA9531</t>
+          <t>VGASN0725QA9930;VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
+          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840;VGASN0725QA9531</t>
+          <t>VGASN0725QA9930;VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
+          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840;VGASN0725QA9531</t>
+          <t>VGASN0725QA9930;VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
+          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840;VGASN0725QA9531</t>
+          <t>VGASN0725QA9930;VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
+          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840;VGASN0725QA9531</t>
+          <t>VGASN0725QA9930;VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
+          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA7840;VGASN0725QA9531</t>
+          <t>VGASN0725QA9930;VGASN0725QA8371</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA6990;00V07252025QA2271;00V07252025QA1452;00V07252025QA9213;00V07252025QA7424;00V07252025QA1235;00V07252025QA2916;00V07252025QA3647;00V07252025QA7468</t>
+          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930;VGASN0725QA8371</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930;VGASN0725QA8371</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930;VGASN0725QA8371</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930;VGASN0725QA8371</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930;VGASN0725QA8371</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0725QA9930;VGASN0725QA8371</t>
+          <t>VGASN0729QA2750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07252025QA8610;00V07252025QA2461;00V07252025QA5842;00V07252025QA4313</t>
+          <t>00V07292025QA3880</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420;VGASN0729QA2901</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420;VGASN0729QA2901</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420;VGASN0729QA2901</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420;VGASN0729QA2901</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420;VGASN0729QA2901</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA2750</t>
+          <t>VGASN0729QA6420;VGASN0729QA2901</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA3880</t>
+          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420;VGASN0729QA2901</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
+          <t>00V07312025QA6360;00V07312025QA7221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420;VGASN0729QA2901</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
+          <t>00V07312025QA6360;00V07312025QA7221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420;VGASN0729QA2901</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
+          <t>00V07312025QA6360;00V07312025QA7221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420;VGASN0729QA2901</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
+          <t>00V07312025QA6360;00V07312025QA7221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420;VGASN0729QA2901</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
+          <t>00V07312025QA6360;00V07312025QA7221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0729QA6420;VGASN0729QA2901</t>
+          <t>81ASN0731QA1150</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07292025QA2670;00V07292025QA1311;00V07292025QA6122;00V07292025QA7733;00V07292025QA8724;00V07292025QA2235;00V07292025QA2736;00V07292025QA1897</t>
+          <t>00V07312025QA6360;00V07312025QA7221</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360;00V07312025QA7221</t>
+          <t>00V07312025QA2460;00V07312025QA6401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360;00V07312025QA7221</t>
+          <t>00V07312025QA2460;00V07312025QA6401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360;00V07312025QA7221</t>
+          <t>00V07312025QA2460;00V07312025QA6401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360;00V07312025QA7221</t>
+          <t>00V07312025QA2460;00V07312025QA6401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360;00V07312025QA7221</t>
+          <t>00V07312025QA2460;00V07312025QA6401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA1150</t>
+          <t>81ASN0731QA5700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA6360;00V07312025QA7221</t>
+          <t>00V07312025QA2460;00V07312025QA6401</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460;00V07312025QA6401</t>
+          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460;00V07312025QA6401</t>
+          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460;00V07312025QA6401</t>
+          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460;00V07312025QA6401</t>
+          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460;00V07312025QA6401</t>
+          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0731QA5700</t>
+          <t>81ASN0803QA2340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V07312025QA2460;00V07312025QA6401</t>
+          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GoodsHolderAnnounced" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GoodsHolderWeighed" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PutawayTaskComplete" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MHEJournal" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,12 +474,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,12 +542,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -609,12 +610,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,12 +678,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -745,12 +746,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -813,12 +814,80 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ASN0803QA2340</t>
+          <t>VGASN0805QA5760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08032025QA7350;00V08032025QA5991;00V08032025QA2232;00V08032025QA6313</t>
+          <t>00V08052025QA6610</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASNID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LPNID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pre_Allocate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VGASN0805QA5760</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>00V08052025QA6610</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -474,17 +479,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -499,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +538,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -542,17 +557,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -567,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,6 +616,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -610,17 +635,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -635,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +694,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -678,17 +713,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -703,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +772,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -746,17 +791,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -771,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +850,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -814,17 +869,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -839,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,6 +928,11 @@
           <t>Pre_Allocate</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -882,17 +947,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA5760</t>
+          <t>VGASN0805QA1800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA6610</t>
+          <t>00V08052025QA2580</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA1800</t>
+          <t>VGASN0805QA6800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA2580</t>
+          <t>00V08052025QA8920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/J30/Input_files/WorkSheet1.xlsx
+++ b/J30/Input_files/WorkSheet1.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGASN0805QA6800</t>
+          <t>VGASN0806QA1970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00V08052025QA8920</t>
+          <t>00V08062025QA7480</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
